--- a/12600516.xlsx
+++ b/12600516.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a0ca02b0b655718c/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\takhi\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="209" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{05F07B4E-9958-48F8-9F13-B6359A045AE4}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C69C766-3EBA-4237-AE42-6B10D535F6BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="61">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -498,10 +498,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -1839,25 +1835,47 @@
       <c r="N24" s="17"/>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A25" s="13"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="15" t="str">
+      <c r="A25" s="13">
+        <v>46270</v>
+      </c>
+      <c r="B25" s="14">
+        <v>300</v>
+      </c>
+      <c r="C25" s="14">
+        <v>38</v>
+      </c>
+      <c r="D25" s="14">
+        <v>120</v>
+      </c>
+      <c r="E25" s="14">
+        <v>20</v>
+      </c>
+      <c r="F25" s="14">
+        <v>0</v>
+      </c>
+      <c r="G25" s="14">
+        <v>0</v>
+      </c>
+      <c r="H25" s="14">
+        <v>0</v>
+      </c>
+      <c r="I25" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J25" s="15" t="str">
+        <v>478</v>
+      </c>
+      <c r="J25" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
-      <c r="M25" s="16"/>
+        <v>962</v>
+      </c>
+      <c r="K25" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L25" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M25" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N25" s="17"/>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">

--- a/12600516.xlsx
+++ b/12600516.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\takhi\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C69C766-3EBA-4237-AE42-6B10D535F6BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A188382-115E-46B8-AD20-47951FB7B30E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="61">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1879,25 +1879,47 @@
       <c r="N25" s="17"/>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A26" s="13"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="15" t="str">
+      <c r="A26" s="13">
+        <v>46271</v>
+      </c>
+      <c r="B26" s="14">
+        <v>340</v>
+      </c>
+      <c r="C26" s="14">
+        <v>40</v>
+      </c>
+      <c r="D26" s="14">
+        <v>100</v>
+      </c>
+      <c r="E26" s="14">
+        <v>34</v>
+      </c>
+      <c r="F26" s="14">
+        <v>0</v>
+      </c>
+      <c r="G26" s="14">
+        <v>0</v>
+      </c>
+      <c r="H26" s="14">
+        <v>0</v>
+      </c>
+      <c r="I26" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J26" s="15" t="str">
+        <v>514</v>
+      </c>
+      <c r="J26" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-      <c r="M26" s="16"/>
+        <v>926</v>
+      </c>
+      <c r="K26" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L26" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M26" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N26" s="17"/>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">

--- a/12600516.xlsx
+++ b/12600516.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\takhi\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A188382-115E-46B8-AD20-47951FB7B30E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8992CDB-F698-4267-9EB8-AEFD3C62FAFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="62">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -218,6 +218,9 @@
   </si>
   <si>
     <t>High</t>
+  </si>
+  <si>
+    <t>Very Satisfied</t>
   </si>
 </sst>
 </file>
@@ -1923,25 +1926,47 @@
       <c r="N26" s="17"/>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A27" s="13"/>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="15" t="str">
+      <c r="A27" s="13">
+        <v>46272</v>
+      </c>
+      <c r="B27" s="14">
+        <v>200</v>
+      </c>
+      <c r="C27" s="14">
+        <v>0</v>
+      </c>
+      <c r="D27" s="14">
+        <v>400</v>
+      </c>
+      <c r="E27" s="14">
+        <v>0</v>
+      </c>
+      <c r="F27" s="14">
+        <v>0</v>
+      </c>
+      <c r="G27" s="14">
+        <v>0</v>
+      </c>
+      <c r="H27" s="14">
+        <v>0</v>
+      </c>
+      <c r="I27" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J27" s="15" t="str">
+        <v>600</v>
+      </c>
+      <c r="J27" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="16"/>
+        <v>840</v>
+      </c>
+      <c r="K27" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L27" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M27" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N27" s="17"/>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">

--- a/12600516.xlsx
+++ b/12600516.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\takhi\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8992CDB-F698-4267-9EB8-AEFD3C62FAFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1730C7B-D1B5-4D5A-9C5D-ECB5B1337A1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="62">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1970,25 +1970,47 @@
       <c r="N27" s="17"/>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A28" s="13"/>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="15" t="str">
+      <c r="A28" s="13">
+        <v>46273</v>
+      </c>
+      <c r="B28" s="14">
+        <v>350</v>
+      </c>
+      <c r="C28" s="14">
+        <v>30</v>
+      </c>
+      <c r="D28" s="14">
+        <v>300</v>
+      </c>
+      <c r="E28" s="14">
+        <v>50</v>
+      </c>
+      <c r="F28" s="14">
+        <v>350</v>
+      </c>
+      <c r="G28" s="14">
+        <v>7</v>
+      </c>
+      <c r="H28" s="14">
+        <v>0</v>
+      </c>
+      <c r="I28" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J28" s="15" t="str">
+        <v>1080</v>
+      </c>
+      <c r="J28" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="16"/>
+        <v>360</v>
+      </c>
+      <c r="K28" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L28" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M28" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N28" s="17"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">

--- a/12600516.xlsx
+++ b/12600516.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\takhi\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1730C7B-D1B5-4D5A-9C5D-ECB5B1337A1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A9D3B7F-50DF-45FD-80F5-E4DE529D6E80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="62">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2014,25 +2014,47 @@
       <c r="N28" s="17"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A29" s="13"/>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="15" t="str">
+      <c r="A29" s="13">
+        <v>46274</v>
+      </c>
+      <c r="B29" s="14">
+        <v>300</v>
+      </c>
+      <c r="C29" s="14">
+        <v>0</v>
+      </c>
+      <c r="D29" s="14">
+        <v>100</v>
+      </c>
+      <c r="E29" s="14">
+        <v>20</v>
+      </c>
+      <c r="F29" s="14">
+        <v>350</v>
+      </c>
+      <c r="G29" s="14">
+        <v>7</v>
+      </c>
+      <c r="H29" s="14">
+        <v>0</v>
+      </c>
+      <c r="I29" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J29" s="15" t="str">
+        <v>770</v>
+      </c>
+      <c r="J29" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K29" s="16"/>
-      <c r="L29" s="16"/>
-      <c r="M29" s="16"/>
+        <v>670</v>
+      </c>
+      <c r="K29" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L29" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M29" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N29" s="17"/>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">

--- a/12600516.xlsx
+++ b/12600516.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\takhi\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A9D3B7F-50DF-45FD-80F5-E4DE529D6E80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1B8686C-C68A-4A2C-9AF8-E7FD1A331A98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="62">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2058,25 +2058,47 @@
       <c r="N29" s="17"/>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A30" s="13"/>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="15" t="str">
+      <c r="A30" s="13">
+        <v>46275</v>
+      </c>
+      <c r="B30" s="14">
+        <v>320</v>
+      </c>
+      <c r="C30" s="14">
+        <v>0</v>
+      </c>
+      <c r="D30" s="14">
+        <v>40</v>
+      </c>
+      <c r="E30" s="14">
+        <v>30</v>
+      </c>
+      <c r="F30" s="14">
+        <v>200</v>
+      </c>
+      <c r="G30" s="14">
+        <v>4</v>
+      </c>
+      <c r="H30" s="14">
+        <v>0</v>
+      </c>
+      <c r="I30" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J30" s="15" t="str">
+        <v>590</v>
+      </c>
+      <c r="J30" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K30" s="16"/>
-      <c r="L30" s="16"/>
-      <c r="M30" s="16"/>
+        <v>850</v>
+      </c>
+      <c r="K30" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L30" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M30" s="16" t="s">
+        <v>60</v>
+      </c>
       <c r="N30" s="17"/>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">

--- a/12600516.xlsx
+++ b/12600516.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\takhi\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1B8686C-C68A-4A2C-9AF8-E7FD1A331A98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{389E4A15-441E-472C-9947-9D8AE4176BFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="62">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2102,25 +2102,47 @@
       <c r="N30" s="17"/>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A31" s="13"/>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="15" t="str">
+      <c r="A31" s="13">
+        <v>46276</v>
+      </c>
+      <c r="B31" s="14">
+        <v>260</v>
+      </c>
+      <c r="C31" s="14">
+        <v>20</v>
+      </c>
+      <c r="D31" s="14">
+        <v>150</v>
+      </c>
+      <c r="E31" s="14">
+        <v>0</v>
+      </c>
+      <c r="F31" s="14">
+        <v>250</v>
+      </c>
+      <c r="G31" s="14">
+        <v>5</v>
+      </c>
+      <c r="H31" s="14">
+        <v>0</v>
+      </c>
+      <c r="I31" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J31" s="15" t="str">
+        <v>680</v>
+      </c>
+      <c r="J31" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
-      <c r="M31" s="16"/>
+        <v>760</v>
+      </c>
+      <c r="K31" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L31" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M31" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N31" s="17"/>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">

--- a/12600516.xlsx
+++ b/12600516.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\takhi\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{389E4A15-441E-472C-9947-9D8AE4176BFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A137C4B4-A902-4BF1-9C9F-93A3CE424AEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="63">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -221,6 +221,9 @@
   </si>
   <si>
     <t>Very Satisfied</t>
+  </si>
+  <si>
+    <t>Very Unsatisfied</t>
   </si>
 </sst>
 </file>
@@ -2146,25 +2149,47 @@
       <c r="N31" s="17"/>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A32" s="13"/>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="15" t="str">
+      <c r="A32" s="13">
+        <v>46277</v>
+      </c>
+      <c r="B32" s="14">
+        <v>200</v>
+      </c>
+      <c r="C32" s="14">
+        <v>0</v>
+      </c>
+      <c r="D32" s="14">
+        <v>0</v>
+      </c>
+      <c r="E32" s="14">
+        <v>0</v>
+      </c>
+      <c r="F32" s="14">
+        <v>0</v>
+      </c>
+      <c r="G32" s="14">
+        <v>0</v>
+      </c>
+      <c r="H32" s="14">
+        <v>0</v>
+      </c>
+      <c r="I32" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J32" s="15" t="str">
+        <v>200</v>
+      </c>
+      <c r="J32" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K32" s="16"/>
-      <c r="L32" s="16"/>
-      <c r="M32" s="16"/>
+        <v>1240</v>
+      </c>
+      <c r="K32" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L32" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M32" s="16" t="s">
+        <v>59</v>
+      </c>
       <c r="N32" s="17"/>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">

--- a/12600516.xlsx
+++ b/12600516.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\takhi\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A137C4B4-A902-4BF1-9C9F-93A3CE424AEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73C314AF-26BE-4F96-BC7A-A98BDC850293}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="63">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2193,25 +2193,47 @@
       <c r="N32" s="17"/>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A33" s="13"/>
-      <c r="B33" s="14"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="15" t="str">
+      <c r="A33" s="13">
+        <v>46278</v>
+      </c>
+      <c r="B33" s="14">
+        <v>300</v>
+      </c>
+      <c r="C33" s="14">
+        <v>50</v>
+      </c>
+      <c r="D33" s="14">
+        <v>200</v>
+      </c>
+      <c r="E33" s="14">
+        <v>45</v>
+      </c>
+      <c r="F33" s="14">
+        <v>0</v>
+      </c>
+      <c r="G33" s="14">
+        <v>0</v>
+      </c>
+      <c r="H33" s="14">
+        <v>0</v>
+      </c>
+      <c r="I33" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J33" s="15" t="str">
+        <v>595</v>
+      </c>
+      <c r="J33" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K33" s="16"/>
-      <c r="L33" s="16"/>
-      <c r="M33" s="16"/>
+        <v>845</v>
+      </c>
+      <c r="K33" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L33" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M33" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N33" s="17"/>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">

--- a/12600516.xlsx
+++ b/12600516.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\takhi\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73C314AF-26BE-4F96-BC7A-A98BDC850293}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA4F15F1-E9D3-4AED-9A79-A8D18B665715}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="63">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2237,25 +2237,47 @@
       <c r="N33" s="17"/>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A34" s="13"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14"/>
-      <c r="I34" s="15" t="str">
+      <c r="A34" s="13">
+        <v>46279</v>
+      </c>
+      <c r="B34" s="14">
+        <v>340</v>
+      </c>
+      <c r="C34" s="14">
+        <v>60</v>
+      </c>
+      <c r="D34" s="14">
+        <v>160</v>
+      </c>
+      <c r="E34" s="14">
+        <v>60</v>
+      </c>
+      <c r="F34" s="14">
+        <v>200</v>
+      </c>
+      <c r="G34" s="14">
+        <v>4</v>
+      </c>
+      <c r="H34" s="14">
+        <v>0</v>
+      </c>
+      <c r="I34" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J34" s="15" t="str">
+        <v>820</v>
+      </c>
+      <c r="J34" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K34" s="16"/>
-      <c r="L34" s="16"/>
-      <c r="M34" s="16"/>
+        <v>620</v>
+      </c>
+      <c r="K34" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L34" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M34" s="16" t="s">
+        <v>59</v>
+      </c>
       <c r="N34" s="17"/>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">

--- a/12600516.xlsx
+++ b/12600516.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\takhi\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA4F15F1-E9D3-4AED-9A79-A8D18B665715}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C24A07C-A0A2-4DEA-AB7F-C74ACB0B38A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="63">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2281,25 +2281,47 @@
       <c r="N34" s="17"/>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A35" s="13"/>
-      <c r="B35" s="14"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14"/>
-      <c r="I35" s="15" t="str">
+      <c r="A35" s="13">
+        <v>45915</v>
+      </c>
+      <c r="B35" s="14">
+        <v>190</v>
+      </c>
+      <c r="C35" s="14">
+        <v>0</v>
+      </c>
+      <c r="D35" s="14">
+        <v>90</v>
+      </c>
+      <c r="E35" s="14">
+        <v>0</v>
+      </c>
+      <c r="F35" s="14">
+        <v>350</v>
+      </c>
+      <c r="G35" s="14">
+        <v>7</v>
+      </c>
+      <c r="H35" s="14">
+        <v>0</v>
+      </c>
+      <c r="I35" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J35" s="15" t="str">
+        <v>630</v>
+      </c>
+      <c r="J35" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K35" s="16"/>
-      <c r="L35" s="16"/>
-      <c r="M35" s="16"/>
+        <v>810</v>
+      </c>
+      <c r="K35" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L35" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M35" s="16" t="s">
+        <v>59</v>
+      </c>
       <c r="N35" s="17"/>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">

--- a/12600516.xlsx
+++ b/12600516.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\takhi\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C24A07C-A0A2-4DEA-AB7F-C74ACB0B38A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D661B26-6CB9-4889-9145-D7352111184B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="63">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2282,7 +2282,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" s="13">
-        <v>45915</v>
+        <v>46280</v>
       </c>
       <c r="B35" s="14">
         <v>190</v>
@@ -2325,25 +2325,47 @@
       <c r="N35" s="17"/>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A36" s="13"/>
-      <c r="B36" s="14"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14"/>
-      <c r="I36" s="15" t="str">
+      <c r="A36" s="13">
+        <v>46281</v>
+      </c>
+      <c r="B36" s="14">
+        <v>230</v>
+      </c>
+      <c r="C36" s="14">
+        <v>0</v>
+      </c>
+      <c r="D36" s="14">
+        <v>250</v>
+      </c>
+      <c r="E36" s="14">
+        <v>0</v>
+      </c>
+      <c r="F36" s="14">
+        <v>350</v>
+      </c>
+      <c r="G36" s="14">
+        <v>7</v>
+      </c>
+      <c r="H36" s="14">
+        <v>0</v>
+      </c>
+      <c r="I36" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J36" s="15" t="str">
+        <v>830</v>
+      </c>
+      <c r="J36" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K36" s="16"/>
-      <c r="L36" s="16"/>
-      <c r="M36" s="16"/>
+        <v>610</v>
+      </c>
+      <c r="K36" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L36" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M36" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N36" s="17"/>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">

--- a/12600516.xlsx
+++ b/12600516.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\takhi\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D661B26-6CB9-4889-9145-D7352111184B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A8E5CDC-4DA6-428B-97E4-8E3F6C93A1E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="63">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2369,25 +2369,47 @@
       <c r="N36" s="17"/>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A37" s="13"/>
-      <c r="B37" s="14"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="15" t="str">
+      <c r="A37" s="13">
+        <v>46282</v>
+      </c>
+      <c r="B37" s="14">
+        <v>400</v>
+      </c>
+      <c r="C37" s="14">
+        <v>0</v>
+      </c>
+      <c r="D37" s="14">
+        <v>0</v>
+      </c>
+      <c r="E37" s="14">
+        <v>0</v>
+      </c>
+      <c r="F37" s="14">
+        <v>200</v>
+      </c>
+      <c r="G37" s="14">
+        <v>4</v>
+      </c>
+      <c r="H37" s="14">
+        <v>0</v>
+      </c>
+      <c r="I37" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J37" s="15" t="str">
+        <v>600</v>
+      </c>
+      <c r="J37" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K37" s="16"/>
-      <c r="L37" s="16"/>
-      <c r="M37" s="16"/>
+        <v>840</v>
+      </c>
+      <c r="K37" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L37" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M37" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N37" s="17"/>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">

--- a/12600516.xlsx
+++ b/12600516.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\takhi\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A8E5CDC-4DA6-428B-97E4-8E3F6C93A1E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7807E53B-61AF-4664-B164-16C8938A2DDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="63">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2413,25 +2413,47 @@
       <c r="N37" s="17"/>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A38" s="13"/>
-      <c r="B38" s="14"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14"/>
-      <c r="H38" s="14"/>
-      <c r="I38" s="15" t="str">
+      <c r="A38" s="13">
+        <v>46283</v>
+      </c>
+      <c r="B38" s="14">
+        <v>200</v>
+      </c>
+      <c r="C38" s="14">
+        <v>10</v>
+      </c>
+      <c r="D38" s="14">
+        <v>45</v>
+      </c>
+      <c r="E38" s="14">
+        <v>0</v>
+      </c>
+      <c r="F38" s="14">
+        <v>250</v>
+      </c>
+      <c r="G38" s="14">
+        <v>5</v>
+      </c>
+      <c r="H38" s="14">
+        <v>0</v>
+      </c>
+      <c r="I38" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J38" s="15" t="str">
+        <v>505</v>
+      </c>
+      <c r="J38" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K38" s="16"/>
-      <c r="L38" s="16"/>
-      <c r="M38" s="16"/>
+        <v>935</v>
+      </c>
+      <c r="K38" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L38" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M38" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N38" s="17"/>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">

--- a/12600516.xlsx
+++ b/12600516.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\takhi\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7807E53B-61AF-4664-B164-16C8938A2DDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA6E28A7-8AB1-417D-A45A-5E5CA8953A31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="63">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2457,25 +2457,47 @@
       <c r="N38" s="17"/>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A39" s="13"/>
-      <c r="B39" s="14"/>
-      <c r="C39" s="14"/>
-      <c r="D39" s="14"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="14"/>
-      <c r="G39" s="14"/>
-      <c r="H39" s="14"/>
-      <c r="I39" s="15" t="str">
+      <c r="A39" s="13">
+        <v>46284</v>
+      </c>
+      <c r="B39" s="14">
+        <v>300</v>
+      </c>
+      <c r="C39" s="14">
+        <v>0</v>
+      </c>
+      <c r="D39" s="14">
+        <v>0</v>
+      </c>
+      <c r="E39" s="14">
+        <v>20</v>
+      </c>
+      <c r="F39" s="14">
+        <v>0</v>
+      </c>
+      <c r="G39" s="14">
+        <v>0</v>
+      </c>
+      <c r="H39" s="14">
+        <v>0</v>
+      </c>
+      <c r="I39" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J39" s="15" t="str">
+        <v>320</v>
+      </c>
+      <c r="J39" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K39" s="16"/>
-      <c r="L39" s="16"/>
-      <c r="M39" s="16"/>
+        <v>1120</v>
+      </c>
+      <c r="K39" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L39" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M39" s="16" t="s">
+        <v>59</v>
+      </c>
       <c r="N39" s="17"/>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">

--- a/12600516.xlsx
+++ b/12600516.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\takhi\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA6E28A7-8AB1-417D-A45A-5E5CA8953A31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AD5B5D6-4CFD-43C3-92D2-6D88739C832D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="63">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2501,25 +2501,47 @@
       <c r="N39" s="17"/>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A40" s="13"/>
-      <c r="B40" s="14"/>
-      <c r="C40" s="14"/>
-      <c r="D40" s="14"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="14"/>
-      <c r="G40" s="14"/>
-      <c r="H40" s="14"/>
-      <c r="I40" s="15" t="str">
+      <c r="A40" s="13">
+        <v>46285</v>
+      </c>
+      <c r="B40" s="14">
+        <v>246</v>
+      </c>
+      <c r="C40" s="14">
+        <v>72</v>
+      </c>
+      <c r="D40" s="14">
+        <v>100</v>
+      </c>
+      <c r="E40" s="14">
+        <v>50</v>
+      </c>
+      <c r="F40" s="14">
+        <v>0</v>
+      </c>
+      <c r="G40" s="14">
+        <v>0</v>
+      </c>
+      <c r="H40" s="14">
+        <v>0</v>
+      </c>
+      <c r="I40" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J40" s="15" t="str">
+        <v>468</v>
+      </c>
+      <c r="J40" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K40" s="16"/>
-      <c r="L40" s="16"/>
-      <c r="M40" s="16"/>
+        <v>972</v>
+      </c>
+      <c r="K40" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L40" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M40" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N40" s="17"/>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">

--- a/12600516.xlsx
+++ b/12600516.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\takhi\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AD5B5D6-4CFD-43C3-92D2-6D88739C832D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1300DC2A-30E6-4305-9CC3-1BA331E84E66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="63">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2545,25 +2545,47 @@
       <c r="N40" s="17"/>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A41" s="13"/>
-      <c r="B41" s="14"/>
-      <c r="C41" s="14"/>
-      <c r="D41" s="14"/>
-      <c r="E41" s="14"/>
-      <c r="F41" s="14"/>
-      <c r="G41" s="14"/>
-      <c r="H41" s="14"/>
-      <c r="I41" s="15" t="str">
+      <c r="A41" s="13">
+        <v>46286</v>
+      </c>
+      <c r="B41" s="14">
+        <v>390</v>
+      </c>
+      <c r="C41" s="14">
+        <v>0</v>
+      </c>
+      <c r="D41" s="14">
+        <v>40</v>
+      </c>
+      <c r="E41" s="14">
+        <v>0</v>
+      </c>
+      <c r="F41" s="14">
+        <v>200</v>
+      </c>
+      <c r="G41" s="14">
+        <v>4</v>
+      </c>
+      <c r="H41" s="14">
+        <v>0</v>
+      </c>
+      <c r="I41" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J41" s="15" t="str">
+        <v>630</v>
+      </c>
+      <c r="J41" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K41" s="16"/>
-      <c r="L41" s="16"/>
-      <c r="M41" s="16"/>
+        <v>810</v>
+      </c>
+      <c r="K41" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L41" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M41" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N41" s="17"/>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">

--- a/12600516.xlsx
+++ b/12600516.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\takhi\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1300DC2A-30E6-4305-9CC3-1BA331E84E66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E13E7BE3-9DEC-4EB9-88A3-01841D902108}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="63">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2589,25 +2589,47 @@
       <c r="N41" s="17"/>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A42" s="13"/>
-      <c r="B42" s="14"/>
-      <c r="C42" s="14"/>
-      <c r="D42" s="14"/>
-      <c r="E42" s="14"/>
-      <c r="F42" s="14"/>
-      <c r="G42" s="14"/>
-      <c r="H42" s="14"/>
-      <c r="I42" s="15" t="str">
+      <c r="A42" s="13">
+        <v>46287</v>
+      </c>
+      <c r="B42" s="14">
+        <v>230</v>
+      </c>
+      <c r="C42" s="14">
+        <v>0</v>
+      </c>
+      <c r="D42" s="14">
+        <v>0</v>
+      </c>
+      <c r="E42" s="14">
+        <v>0</v>
+      </c>
+      <c r="F42" s="14">
+        <v>350</v>
+      </c>
+      <c r="G42" s="14">
+        <v>7</v>
+      </c>
+      <c r="H42" s="14">
+        <v>0</v>
+      </c>
+      <c r="I42" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J42" s="15" t="str">
+        <v>580</v>
+      </c>
+      <c r="J42" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K42" s="16"/>
-      <c r="L42" s="16"/>
-      <c r="M42" s="16"/>
+        <v>860</v>
+      </c>
+      <c r="K42" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L42" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M42" s="16" t="s">
+        <v>59</v>
+      </c>
       <c r="N42" s="17"/>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">

--- a/12600516.xlsx
+++ b/12600516.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\takhi\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E13E7BE3-9DEC-4EB9-88A3-01841D902108}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1ECEBCC-88C6-452D-901E-F95B8A3F0AF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="64">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -224,6 +224,9 @@
   </si>
   <si>
     <t>Very Unsatisfied</t>
+  </si>
+  <si>
+    <t>Stressed</t>
   </si>
 </sst>
 </file>
@@ -2633,25 +2636,47 @@
       <c r="N42" s="17"/>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A43" s="13"/>
-      <c r="B43" s="14"/>
-      <c r="C43" s="14"/>
-      <c r="D43" s="14"/>
-      <c r="E43" s="14"/>
-      <c r="F43" s="14"/>
-      <c r="G43" s="14"/>
-      <c r="H43" s="14"/>
-      <c r="I43" s="15" t="str">
+      <c r="A43" s="13">
+        <v>46288</v>
+      </c>
+      <c r="B43" s="14">
+        <v>455</v>
+      </c>
+      <c r="C43" s="14">
+        <v>0</v>
+      </c>
+      <c r="D43" s="14">
+        <v>60</v>
+      </c>
+      <c r="E43" s="14">
+        <v>0</v>
+      </c>
+      <c r="F43" s="14">
+        <v>300</v>
+      </c>
+      <c r="G43" s="14">
+        <v>6</v>
+      </c>
+      <c r="H43" s="14">
+        <v>0</v>
+      </c>
+      <c r="I43" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J43" s="15" t="str">
+        <v>815</v>
+      </c>
+      <c r="J43" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K43" s="16"/>
-      <c r="L43" s="16"/>
-      <c r="M43" s="16"/>
+        <v>625</v>
+      </c>
+      <c r="K43" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="L43" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M43" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N43" s="17"/>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
